--- a/data_processed/results_XGB_kWh_electricity_per_capitaincome.xlsx
+++ b/data_processed/results_XGB_kWh_electricity_per_capitaincome.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.9193" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.9318" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -455,10 +455,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22.89082527160645</v>
+        <v>30.78662872314453</v>
       </c>
       <c r="D2" t="n">
-        <v>5.201971530914307</v>
+        <v>6.757081985473633</v>
       </c>
     </row>
     <row r="3">
@@ -471,10 +471,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23.33274078369141</v>
+        <v>44.89569473266602</v>
       </c>
       <c r="D3" t="n">
-        <v>5.302397727966309</v>
+        <v>9.853754043579102</v>
       </c>
     </row>
     <row r="4">
@@ -487,10 +487,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29.67922782897949</v>
+        <v>19.6678409576416</v>
       </c>
       <c r="D4" t="n">
-        <v>6.744645118713379</v>
+        <v>4.316718578338623</v>
       </c>
     </row>
     <row r="5">
@@ -503,10 +503,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13.19073963165283</v>
+        <v>14.84278774261475</v>
       </c>
       <c r="D5" t="n">
-        <v>2.997613668441772</v>
+        <v>3.257710933685303</v>
       </c>
     </row>
     <row r="6">
@@ -515,14 +515,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>distance_train</t>
+          <t>distance_depstore</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>14.94204998016357</v>
+        <v>9.423069000244141</v>
       </c>
       <c r="D6" t="n">
-        <v>3.395601272583008</v>
+        <v>2.068185091018677</v>
       </c>
     </row>
     <row r="7">
@@ -531,14 +531,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>distance_depstore</t>
+          <t>distance_supermarket</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11.78463745117188</v>
+        <v>15.35554599761963</v>
       </c>
       <c r="D7" t="n">
-        <v>2.678075075149536</v>
+        <v>3.370251417160034</v>
       </c>
     </row>
     <row r="8">
@@ -547,14 +547,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>distance_supermarket</t>
+          <t>household_size</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10.26680088043213</v>
+        <v>73.44510650634766</v>
       </c>
       <c r="D8" t="n">
-        <v>2.333144426345825</v>
+        <v>16.11981010437012</v>
       </c>
     </row>
     <row r="9">
@@ -563,14 +563,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>household_size</t>
+          <t>dwelling_size</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>101.8789978027344</v>
+        <v>63.86542892456055</v>
       </c>
       <c r="D9" t="n">
-        <v>23.15214157104492</v>
+        <v>14.01725196838379</v>
       </c>
     </row>
     <row r="10">
@@ -579,14 +579,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>dwelling_size</t>
+          <t>cars_per_adult</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>59.20818328857422</v>
+        <v>93.55483245849609</v>
       </c>
       <c r="D10" t="n">
-        <v>13.45514106750488</v>
+        <v>20.53351402282715</v>
       </c>
     </row>
     <row r="11">
@@ -595,14 +595,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>cars_per_adult</t>
+          <t>heatpump_pc</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>150.2285766601562</v>
+        <v>4.317997455596924</v>
       </c>
       <c r="D11" t="n">
-        <v>34.1396484375</v>
+        <v>0.9477186799049377</v>
       </c>
     </row>
     <row r="12">
@@ -611,14 +611,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>heatpump_pc</t>
+          <t>solarcapacity</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.638553619384766</v>
+        <v>85.46524047851562</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5996149182319641</v>
+        <v>18.75800323486328</v>
       </c>
     </row>
   </sheetData>

--- a/data_processed/results_XGB_kWh_electricity_per_capitaincome.xlsx
+++ b/data_processed/results_XGB_kWh_electricity_per_capitaincome.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.9318" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.9199" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,10 +455,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>30.78662872314453</v>
+        <v>45.98386764526367</v>
       </c>
       <c r="D2" t="n">
-        <v>6.757081985473633</v>
+        <v>10.37457752227783</v>
       </c>
     </row>
     <row r="3">
@@ -467,14 +467,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>building_type</t>
+          <t>household_size</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>44.89569473266602</v>
+        <v>33.48775100708008</v>
       </c>
       <c r="D3" t="n">
-        <v>9.853754043579102</v>
+        <v>7.555285930633545</v>
       </c>
     </row>
     <row r="4">
@@ -483,14 +483,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>building_age</t>
+          <t>dwelling_size</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>19.6678409576416</v>
+        <v>70.08934783935547</v>
       </c>
       <c r="D4" t="n">
-        <v>4.316718578338623</v>
+        <v>15.81309700012207</v>
       </c>
     </row>
     <row r="5">
@@ -499,14 +499,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>population_density</t>
+          <t>building_type</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>14.84278774261475</v>
+        <v>75.36418151855469</v>
       </c>
       <c r="D5" t="n">
-        <v>3.257710933685303</v>
+        <v>17.00317001342773</v>
       </c>
     </row>
     <row r="6">
@@ -515,14 +515,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>distance_depstore</t>
+          <t>building_age</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9.423069000244141</v>
+        <v>11.17964458465576</v>
       </c>
       <c r="D6" t="n">
-        <v>2.068185091018677</v>
+        <v>2.52227783203125</v>
       </c>
     </row>
     <row r="7">
@@ -531,14 +531,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>distance_supermarket</t>
+          <t>population_density</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>15.35554599761963</v>
+        <v>10.98456764221191</v>
       </c>
       <c r="D7" t="n">
-        <v>3.370251417160034</v>
+        <v>2.478265762329102</v>
       </c>
     </row>
     <row r="8">
@@ -547,14 +547,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>household_size</t>
+          <t>distance_supermarket</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>73.44510650634766</v>
+        <v>16.06064033508301</v>
       </c>
       <c r="D8" t="n">
-        <v>16.11981010437012</v>
+        <v>3.623496055603027</v>
       </c>
     </row>
     <row r="9">
@@ -563,14 +563,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>dwelling_size</t>
+          <t>distance_depstore</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>63.86542892456055</v>
+        <v>10.50069618225098</v>
       </c>
       <c r="D9" t="n">
-        <v>14.01725196838379</v>
+        <v>2.369097948074341</v>
       </c>
     </row>
     <row r="10">
@@ -579,14 +579,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>cars_per_adult</t>
+          <t>heatpump_pc</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>93.55483245849609</v>
+        <v>7.677135467529297</v>
       </c>
       <c r="D10" t="n">
-        <v>20.53351402282715</v>
+        <v>1.732064843177795</v>
       </c>
     </row>
     <row r="11">
@@ -595,30 +595,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>heatpump_pc</t>
+          <t>solarcapacity</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4.317997455596924</v>
+        <v>161.9082336425781</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9477186799049377</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>solarcapacity</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>85.46524047851562</v>
-      </c>
-      <c r="D12" t="n">
-        <v>18.75800323486328</v>
+        <v>36.52866744995117</v>
       </c>
     </row>
   </sheetData>
